--- a/cards.xlsx
+++ b/cards.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tanvir Hasan\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tanvir Hasan\Documents\GitHub\bitr0w.github.io\bitr0w.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EBCC08C-F58F-4CE8-8679-0FA9EABA9686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEC5E6E-B82B-4883-A340-D595ACBEC0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Title</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t>Coming soon!!</t>
+  </si>
+  <si>
+    <t>Date</t>
   </si>
 </sst>
 </file>
@@ -90,11 +93,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -433,30 +438,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.5703125" customWidth="1"/>
     <col min="2" max="2" width="134.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
+      </c>
+      <c r="C2" s="3">
+        <v>45774</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/cards.xlsx
+++ b/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tanvir Hasan\Documents\GitHub\bitr0w.github.io\bitr0w.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEC5E6E-B82B-4883-A340-D595ACBEC0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C1A937-CB62-4A4C-8CAD-DCED96C37175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Title</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>"27/04/2025"</t>
   </si>
 </sst>
 </file>
@@ -464,8 +467,8 @@
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3">
-        <v>45774</v>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/cards.xlsx
+++ b/cards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tanvir Hasan\Documents\GitHub\bitr0w.github.io\bitr0w.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C1A937-CB62-4A4C-8CAD-DCED96C37175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DB1F63-2654-467B-BF58-C0AB826AE937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,13 +31,13 @@
     <t>English(Sillabus)</t>
   </si>
   <si>
-    <t>Coming soon!!</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
     <t>"27/04/2025"</t>
+  </si>
+  <si>
+    <t>•The best christmas present…&lt;br&gt;•The ant and the cricket&lt;br&gt;•How the camel got his hump</t>
   </si>
 </sst>
 </file>
@@ -121,9 +121,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -161,9 +161,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -196,26 +196,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -248,26 +231,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -457,7 +423,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -465,10 +431,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/cards.xlsx
+++ b/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tanvir Hasan\Documents\GitHub\bitr0w.github.io\bitr0w.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DB1F63-2654-467B-BF58-C0AB826AE937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3D7A3C-6FDE-4637-AAFA-D56F062492BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Title</t>
   </si>
@@ -28,16 +28,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>English(Sillabus)</t>
+    <t>Maths(Syllabus)</t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>"27/04/2025"</t>
-  </si>
-  <si>
-    <t>•The best christmas present…&lt;br&gt;•The ant and the cricket&lt;br&gt;•How the camel got his hump</t>
+    <t>English(Syllabus)</t>
   </si>
 </sst>
 </file>
@@ -407,12 +401,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.5703125" customWidth="1"/>
     <col min="2" max="2" width="134.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -422,19 +416,17 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/cards.xlsx
+++ b/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tanvir Hasan\Documents\GitHub\bitr0w.github.io\bitr0w.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3D7A3C-6FDE-4637-AAFA-D56F062492BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86174FB-11F9-498B-A95C-AA093B09BC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Title</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t>English(Syllabus)</t>
+  </si>
+  <si>
+    <t>•The ant and the cricket &lt;br&gt; •The best christmas present… &lt;br&gt; •The tsunami</t>
   </si>
 </sst>
 </file>
@@ -422,6 +425,9 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">

--- a/cards.xlsx
+++ b/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tanvir Hasan\Documents\GitHub\bitr0w.github.io\bitr0w.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86174FB-11F9-498B-A95C-AA093B09BC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DEB4EE4-3F62-4807-91E7-C3378B023832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/cards.xlsx
+++ b/cards.xlsx
@@ -1,26 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tanvir Hasan\Documents\GitHub\bitr0w.github.io\bitr0w.github.io\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tanvir Hasan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DEB4EE4-3F62-4807-91E7-C3378B023832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DA6006-AAAB-489D-80B7-D8C017134355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Title</t>
   </si>
@@ -28,29 +39,39 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Maths(Syllabus)</t>
-  </si>
-  <si>
-    <t>English(Syllabus)</t>
-  </si>
-  <si>
-    <t>•The ant and the cricket &lt;br&gt; •The best christmas present… &lt;br&gt; •The tsunami</t>
+    <t>Attachment</t>
+  </si>
+  <si>
+    <t>Card 1</t>
+  </si>
+  <si>
+    <t>Something useful</t>
+  </si>
+  <si>
+    <t>files/sample.pdf</t>
+  </si>
+  <si>
+    <t>Card 2</t>
+  </si>
+  <si>
+    <t>No attachment</t>
+  </si>
+  <si>
+    <t>Card 3</t>
+  </si>
+  <si>
+    <t>Another file here</t>
+  </si>
+  <si>
+    <t>files/data.txt</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -66,7 +87,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -74,32 +95,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -118,9 +119,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -158,7 +159,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -192,7 +193,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -227,10 +227,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -404,22 +403,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.5703125" customWidth="1"/>
-    <col min="2" max="2" width="134.42578125" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+    <col min="3" max="3" width="39" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -428,15 +429,30 @@
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cards.xlsx
+++ b/cards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tanvir Hasan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tanvir\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DA6006-AAAB-489D-80B7-D8C017134355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D9B9491-2169-40A9-9B10-1767A661C21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t>Title</t>
   </si>
@@ -42,28 +42,16 @@
     <t>Attachment</t>
   </si>
   <si>
-    <t>Card 1</t>
-  </si>
-  <si>
-    <t>Something useful</t>
-  </si>
-  <si>
-    <t>files/sample.pdf</t>
-  </si>
-  <si>
-    <t>Card 2</t>
-  </si>
-  <si>
-    <t>No attachment</t>
-  </si>
-  <si>
-    <t>Card 3</t>
-  </si>
-  <si>
-    <t>Another file here</t>
-  </si>
-  <si>
-    <t>files/data.txt</t>
+    <t>English(Syllybus)</t>
+  </si>
+  <si>
+    <t>Maths(Syllybus)</t>
+  </si>
+  <si>
+    <t>Computer(syllybus)</t>
+  </si>
+  <si>
+    <t>coming soon(31/05/2025)</t>
   </si>
 </sst>
 </file>
@@ -427,29 +415,23 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/cards.xlsx
+++ b/cards.xlsx
@@ -1,37 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tanvir\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D9B9491-2169-40A9-9B10-1767A661C21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F1E4090-3FB0-48C4-9CBF-A26B4185F802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>Date</t>
+  </si>
   <si>
     <t>Title</t>
   </si>
@@ -39,27 +31,65 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Attachment</t>
-  </si>
-  <si>
-    <t>English(Syllybus)</t>
-  </si>
-  <si>
-    <t>Maths(Syllybus)</t>
-  </si>
-  <si>
-    <t>Computer(syllybus)</t>
-  </si>
-  <si>
-    <t>coming soon(31/05/2025)</t>
+    <t>2025-01-10</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>2025-03-12</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>2025-05-20</t>
+  </si>
+  <si>
+    <t>Math Exam</t>
+  </si>
+  <si>
+    <t>Science Fair</t>
+  </si>
+  <si>
+    <t>History Assignment</t>
+  </si>
+  <si>
+    <t>Sports Day</t>
+  </si>
+  <si>
+    <t>Parent-Teacher Meeting</t>
+  </si>
+  <si>
+    <t>Chapters 1–5 from NCERT book. Bring geometry box.</t>
+  </si>
+  <si>
+    <t>Group project presentation on renewable energy sources.</t>
+  </si>
+  <si>
+    <t>Submit a report on Indian Freedom Movement.</t>
+  </si>
+  <si>
+    <t>Wear house T-shirts. Participation is compulsory.</t>
+  </si>
+  <si>
+    <t>All parents to attend. Time: 9:00 AM - 12:00 PM.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -75,7 +105,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -83,12 +113,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -107,9 +155,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -147,7 +195,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -181,6 +229,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -215,9 +264,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -391,22 +441,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.140625" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" customWidth="1"/>
-    <col min="3" max="3" width="39" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="34.85546875" customWidth="1"/>
+    <col min="3" max="3" width="113.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -415,7 +465,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -423,7 +476,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -431,10 +487,35 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>